--- a/reports/pdf_rolling5_20260826.xlsx
+++ b/reports/pdf_rolling5_20260826.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-08-19 ~ 2026-08-26  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-08-19 ~ 2026-08-26  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,456억   ·   현금 65억(1.5%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 9종목  /  매도 21종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,456억   ·   현금 81억(1.7%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 10종목  /  매도 21종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,11 +665,11 @@
         <v>454</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>11877548000</v>
+        <v>12111358000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.69%</t>
+          <t>0.00%→2.66%</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -686,11 +686,11 @@
         <v>-139</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1352956500</v>
+        <v>-1411656200</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>0.70%→0.37%</t>
+          <t>0.70%→0.38%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
@@ -709,11 +709,11 @@
         <v>196</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>8872626000</v>
+        <v>9791180000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.01%</t>
+          <t>0.00%→2.15%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -730,11 +730,11 @@
         <v>-101</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1200506200</v>
+        <v>-1257722700</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>0.82%→0.41%</t>
+          <t>0.82%→0.42%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
@@ -746,44 +746,44 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>큐리언트</t>
+          <t>하림지주</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2361223500</v>
+        <v>1390870800</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>1.25%→1.90%</t>
+          <t>0.59%→0.92%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>222→309</t>
+          <t>244→365</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-46</v>
+        <v>-99</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1634610000</v>
+        <v>-6872778000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>1.48%→0.96%</t>
+          <t>6.18%→4.55%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>165→119</t>
+          <t>398→299</t>
         </is>
       </c>
     </row>
@@ -794,151 +794,151 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2303183000</v>
+        <v>3712635000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.52%</t>
+          <t>0.00%→0.81%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>0→59</t>
+          <t>0→89</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-45</v>
+        <v>-98</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-3480885000</v>
+        <v>-1291022600</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.94%→0.12%</t>
+          <t>0.69%→0.30%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>52→7</t>
+          <t>201→103</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>하림지주</t>
+          <t>큐리언트</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>484532600</v>
+        <v>2244730500</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>0.59%→0.73%</t>
+          <t>1.25%→1.75%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>244→287</t>
+          <t>222→309</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>두산테스나  (편출)</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-32</v>
+        <v>-52</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-2129216000</v>
+        <v>-4215172000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>6.18%→5.51%</t>
+          <t>0.94%→0.00%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>398→366</t>
+          <t>52→0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>티씨케이  (신규)</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>451346000</v>
+        <v>4477410000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.31%→0.41%</t>
+          <t>0.00%→0.98%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>42→56</t>
+          <t>0→18</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-31</v>
+        <v>-46</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-425626900</v>
+        <v>-1781488000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.69%→0.53%</t>
+          <t>1.48%→1.01%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>201→170</t>
+          <t>165→119</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>3301150000</v>
+        <v>460719000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>5.94%→7.24%</t>
+          <t>0.31%→0.40%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>87→97</t>
+          <t>42→56</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티씨케이  (신규)</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2108925000</v>
+        <v>3146650000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.48%</t>
+          <t>5.94%→6.69%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>0→9</t>
+          <t>87→97</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -994,11 +994,11 @@
         <v>-26</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-969436000</v>
+        <v>-961402000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.49%→0.30%</t>
+          <t>0.49%→0.29%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
@@ -1017,11 +1017,11 @@
         <v>9</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1021554000</v>
+        <v>989109000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>1.15%→1.51%</t>
+          <t>1.15%→1.42%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -1038,11 +1038,11 @@
         <v>-23</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-424998600</v>
+        <v>-419076100</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>3.87%→3.19%</t>
+          <t>3.87%→3.05%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
@@ -1052,11 +1052,27 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>827296000</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>0.85%→0.98%</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>35→43</t>
+        </is>
+      </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
           <t>에이비엘바이오</t>
@@ -1066,11 +1082,11 @@
         <v>-22</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1717628000</v>
+        <v>-1690436000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.92%→1.47%</t>
+          <t>1.92%→1.40%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
@@ -1094,11 +1110,11 @@
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-403760000</v>
+        <v>-444136000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.93%→0.77%</t>
+          <t>0.93%→0.82%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
@@ -1115,23 +1131,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1300272000</v>
+        <v>-433836000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>4.68%→4.21%</t>
+          <t>1.50%→1.28%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>184→172</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
@@ -1143,23 +1159,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-433836000</v>
+        <v>-1444884000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.50%→1.32%</t>
+          <t>4.68%→4.54%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>184→172</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1194,7 @@
         <v>-11</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-204506500</v>
+        <v>-210398100</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1206,11 +1222,11 @@
         <v>-8</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-367504000</v>
+        <v>-357204000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.59%</t>
+          <t>0.58%→0.56%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
@@ -1234,11 +1250,11 @@
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-196472500</v>
+        <v>-212334500</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.48%</t>
+          <t>0.58%→0.51%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
@@ -1262,11 +1278,11 @@
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-903413000</v>
+        <v>-936579000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>2.30%→2.01%</t>
+          <t>2.30%→2.02%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
@@ -1290,11 +1306,11 @@
         <v>-6</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-824412000</v>
+        <v>-859020000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>6.59%→6.06%</t>
+          <t>6.59%→6.12%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
@@ -1311,23 +1327,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-451140000</v>
+        <v>-1313250000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.62%→0.53%</t>
+          <t>3.52%→2.88%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>31→26</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1355,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-1274625000</v>
+        <v>-451655000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>3.52%→2.88%</t>
+          <t>0.62%→0.51%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>31→26</t>
         </is>
       </c>
     </row>
@@ -1374,11 +1390,11 @@
         <v>-4</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-423948000</v>
+        <v>-410764000</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>1.66%→1.56%</t>
+          <t>1.66%→1.46%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
@@ -1390,7 +1406,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,915억   ·   현금 39억(1.0%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 7종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,915억   ·   현금 38억(1.0%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 7종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1486,11 +1502,11 @@
         <v>140</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1113525000</v>
+        <v>1217160000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>1.05%→1.16%</t>
+          <t>1.05%→1.29%</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -1530,11 +1546,11 @@
         <v>69</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>722326500</v>
+        <v>705300750</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>3.63%→2.89%</t>
+          <t>3.63%→2.88%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1555,7 +1571,7 @@
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>0.69%→0.54%</t>
+          <t>0.69%→0.55%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
@@ -1574,11 +1590,11 @@
         <v>50</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>791437500</v>
+        <v>742875000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>2.48%→2.71%</t>
+          <t>2.48%→2.60%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -1595,11 +1611,11 @@
         <v>-6</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-1009575000</v>
+        <v>-962325000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>9.30%→9.56%</t>
+          <t>9.30%→9.30%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -1618,11 +1634,11 @@
         <v>24</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>753480000</v>
+        <v>764820000</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>5.34%→5.54%</t>
+          <t>5.34%→5.74%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1646,11 +1662,11 @@
         <v>18</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>716310000</v>
+        <v>704970000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>8.78%→8.37%</t>
+          <t>8.78%→8.41%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -1674,11 +1690,11 @@
         <v>13</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>697515000</v>
+        <v>685230000</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>7.94%→7.66%</t>
+          <t>7.94%→7.68%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -1702,11 +1718,11 @@
         <v>3</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>655200000</v>
+        <v>652837500</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>4.88%→5.24%</t>
+          <t>4.88%→5.33%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -1721,881 +1737,1721 @@
       <c r="K37" s="17" t="n"/>
     </row>
     <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="n"/>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="19" t="n"/>
-      <c r="F39" s="19" t="n"/>
-      <c r="G39" s="19" t="n"/>
-      <c r="H39" s="19" t="n"/>
-      <c r="I39" s="19" t="n"/>
-      <c r="J39" s="19" t="n"/>
-      <c r="K39" s="19" t="n"/>
-    </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B41" s="19" t="n"/>
-      <c r="C41" s="19" t="n"/>
-      <c r="D41" s="19" t="n"/>
-      <c r="E41" s="19" t="n"/>
-      <c r="F41" s="19" t="n"/>
-      <c r="G41" s="19" t="n"/>
-      <c r="H41" s="19" t="n"/>
-      <c r="I41" s="19" t="n"/>
-      <c r="J41" s="19" t="n"/>
-      <c r="K41" s="19" t="n"/>
-    </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억   ·   현금 3억(1.2%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 11종목  /  매도 9종목</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n"/>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억   ·   현금 64억(2.4%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 6종목  /  매도 8종목</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>아이티센글로벌  (신규)</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>110</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>3127410000</v>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.21%</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>0→110</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>-158</v>
+      </c>
+      <c r="I42" s="15" t="n">
+        <v>-1497366000</v>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>1.07%→0.55%</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>308→150</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>5005891800</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>4.44%→6.67%</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>149→210</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>더블유씨피  (편출)</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>-144</v>
+      </c>
+      <c r="I43" s="15" t="n">
+        <v>-898672320</v>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>0.34%→0.00%</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>144→0</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-      <c r="J44" s="8" t="n"/>
-      <c r="K44" s="8" t="n"/>
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>1480096800</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>1.12%→1.64%</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>39→60</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>PS일렉트로닉스  (편출)</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>-116</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>-785818800</v>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>0.30%→0.00%</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>116→0</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G45" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H45" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K45" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>3495960000</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>1.08%→2.37%</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>15→35</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>메쥬  (편출)</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>-77</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>-640539900</v>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>0.25%→0.00%</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>77→0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>코미코  (신규)</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
-        <v>357</v>
+        <v>13</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>671017200</v>
+        <v>179599680</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.47%</t>
+          <t>1.61%→1.94%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>0→357</t>
+          <t>350→363</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>더블유씨피</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-71</v>
+        <v>-50</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-47338540</v>
+        <v>-738855000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>7.67%→7.30%</t>
+          <t>0.60%→0.40%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>3,052→2,981</t>
+          <t>120→70</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>이오테크닉스  (신규)</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>119513700</v>
+        <v>3382236000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>3.16%→3.52%</t>
+          <t>0.00%→1.31%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>680→777</t>
+          <t>0→12</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-49</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-44164680</v>
+        <v>-2211791400</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>3.08%→2.84%</t>
+          <t>1.63%→0.70%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>907→858</t>
+          <t>89→40</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>노바렉스</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="n">
-        <v>82</v>
-      </c>
-      <c r="C48" s="11" t="n">
-        <v>67536840</v>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>0.16%→0.40%</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>51→133</t>
-        </is>
-      </c>
+      <c r="A48" s="17" t="n"/>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-37</v>
+        <v>-42</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-104454700</v>
+        <v>-1500735600</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>8.09%→7.51%</t>
+          <t>4.94%→4.13%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>761→724</t>
+          <t>341→299</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>코스맥스엔비티</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="C49" s="11" t="n">
-        <v>42430860</v>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>0.28%→0.43%</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>122→191</t>
-        </is>
-      </c>
+      <c r="A49" s="17" t="n"/>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-35</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-93758000</v>
+        <v>-7506135000</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>3.38%→2.95%</t>
+          <t>6.64%→3.98%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>335→300</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>스피어</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="C50" s="11" t="n">
-        <v>44348200</v>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>2.36%→2.46%</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>367→393</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>덕산하이메탈</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>-23776200</v>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>0.60%→0.50%</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
-        <is>
-          <t>227→193</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>53235600</v>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>2.80%→2.93%</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>307→329</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I51" s="15" t="n">
-        <v>-87823200</v>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>1.06%→0.71%</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>77→53</t>
-        </is>
-      </c>
+          <t>83→48</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,255억   ·   현금 63억(2.8%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 4종목  /  매도 11종목</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>오름테라퓨틱  (신규)</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>118030000</v>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.43%</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>0→22</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>디앤디파마텍</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>-17</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <v>-72083400</v>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>0.48%→0.20%</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>30→13</t>
-        </is>
-      </c>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="8" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>엘티씨</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="C53" s="11" t="n">
-        <v>41558400</v>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>1.02%→1.15%</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>104→120</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>HPSP</t>
-        </is>
-      </c>
-      <c r="H53" s="15" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I53" s="15" t="n">
-        <v>-52036800</v>
-      </c>
-      <c r="J53" s="16" t="inlineStr">
-        <is>
-          <t>1.48%→1.25%</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>121→105</t>
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
-        <v>7</v>
+        <v>296</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>54182800</v>
+        <v>6054946400</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.19%</t>
+          <t>1.81%→4.67%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>35→42</t>
+          <t>200→496</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>에이프릴바이오</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-3</v>
+        <v>-218</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-34232400</v>
+        <v>-1430383020</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>1.76%→1.59%</t>
+          <t>1.93%→0.78%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>41→38</t>
+          <t>475→257</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
-        <v>5</v>
+        <v>279</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>40774000</v>
+        <v>6647426100</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>3.13%→3.21%</t>
+          <t>1.53%→4.71%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>102→107</t>
-        </is>
-      </c>
-      <c r="G55" s="17" t="n"/>
-      <c r="H55" s="17" t="n"/>
-      <c r="I55" s="17" t="n"/>
-      <c r="J55" s="17" t="n"/>
-      <c r="K55" s="17" t="n"/>
+          <t>151→430</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>고영  (편출)</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-194</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-1980953400</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>0.90%→0.00%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>194→0</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>보로노이  (신규)</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>24804800</v>
+        <v>3172383200</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.09%</t>
+          <t>2.69%→4.07%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>0→2</t>
-        </is>
-      </c>
-      <c r="G56" s="17" t="n"/>
-      <c r="H56" s="17" t="n"/>
-      <c r="I56" s="17" t="n"/>
-      <c r="J56" s="17" t="n"/>
-      <c r="K56" s="17" t="n"/>
-    </row>
-    <row r="58" ht="19" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 560억   ·   현금 6억(1.1%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 4종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="4" t="n"/>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n"/>
-      <c r="I58" s="4" t="n"/>
-      <c r="J58" s="4" t="n"/>
-      <c r="K58" s="4" t="n"/>
+          <t>100→156</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-183</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-6580295700</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>3.86%→1.11%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>250→67</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>4052088000</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>5.13%→8.47%</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>85→109</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-125</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-4199862500</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>6.29%→4.08%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>389→264</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="n"/>
+      <c r="B58" s="17" t="n"/>
+      <c r="C58" s="17" t="n"/>
+      <c r="D58" s="17" t="n"/>
+      <c r="E58" s="17" t="n"/>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>케어젠  (편출)</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>-102</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>-1904319600</v>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>0.87%→0.00%</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>102→0</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="8" t="n"/>
-      <c r="J59" s="8" t="n"/>
-      <c r="K59" s="8" t="n"/>
+      <c r="A59" s="17" t="n"/>
+      <c r="B59" s="17" t="n"/>
+      <c r="C59" s="17" t="n"/>
+      <c r="D59" s="17" t="n"/>
+      <c r="E59" s="17" t="n"/>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>에임드바이오</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>-101</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>-884962000</v>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>0.81%→0.41%</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>203→102</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J60" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K60" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A60" s="17" t="n"/>
+      <c r="B60" s="17" t="n"/>
+      <c r="C60" s="17" t="n"/>
+      <c r="D60" s="17" t="n"/>
+      <c r="E60" s="17" t="n"/>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>지아이이노베이션</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-80</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-215680000</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>0.25%→0.15%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>199→119</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>프로티나  (신규)</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="n">
-        <v>227</v>
-      </c>
-      <c r="C61" s="11" t="n">
-        <v>912301650</v>
-      </c>
-      <c r="D61" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→1.64%</t>
-        </is>
-      </c>
-      <c r="E61" s="13" t="inlineStr">
-        <is>
-          <t>0→227</t>
-        </is>
-      </c>
+      <c r="A61" s="17" t="n"/>
+      <c r="B61" s="17" t="n"/>
+      <c r="C61" s="17" t="n"/>
+      <c r="D61" s="17" t="n"/>
+      <c r="E61" s="17" t="n"/>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>에이프릴바이오</t>
+          <t>앱클론</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
-        <v>-230</v>
+        <v>-67</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-536585400</v>
+        <v>-638985700</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2.62%→0.98%</t>
+          <t>0.68%→0.36%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>464→234</t>
+          <t>150→83</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="n">
-        <v>223</v>
-      </c>
-      <c r="C62" s="11" t="n">
-        <v>395278650</v>
-      </c>
-      <c r="D62" s="12" t="inlineStr">
-        <is>
-          <t>2.52%→2.79%</t>
-        </is>
-      </c>
-      <c r="E62" s="13" t="inlineStr">
-        <is>
-          <t>655→878</t>
-        </is>
-      </c>
+      <c r="A62" s="17" t="n"/>
+      <c r="B62" s="17" t="n"/>
+      <c r="C62" s="17" t="n"/>
+      <c r="D62" s="17" t="n"/>
+      <c r="E62" s="17" t="n"/>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>리브스메드</t>
+          <t>토모큐브</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
-        <v>-116</v>
+        <v>-41</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-475698600</v>
+        <v>-431781250</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>2.90%→1.71%</t>
+          <t>0.51%→0.29%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>349→233</t>
+          <t>101→60</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>알지노믹스</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="n">
-        <v>74</v>
-      </c>
-      <c r="C63" s="11" t="n">
-        <v>270995400</v>
-      </c>
-      <c r="D63" s="12" t="inlineStr">
-        <is>
-          <t>3.42%→3.76%</t>
-        </is>
-      </c>
-      <c r="E63" s="13" t="inlineStr">
-        <is>
-          <t>498→572</t>
-        </is>
-      </c>
+      <c r="A63" s="17" t="n"/>
+      <c r="B63" s="17" t="n"/>
+      <c r="C63" s="17" t="n"/>
+      <c r="D63" s="17" t="n"/>
+      <c r="E63" s="17" t="n"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>네이처셀</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
-        <v>-91</v>
+        <v>-29</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-196437150</v>
+        <v>-242859050</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>1.77%→1.20%</t>
+          <t>0.16%→0.07%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>402→311</t>
+          <t>46→17</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>에스티팜</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C64" s="11" t="n">
-        <v>283654800</v>
-      </c>
-      <c r="D64" s="12" t="inlineStr">
-        <is>
-          <t>5.50%→6.43%</t>
-        </is>
-      </c>
-      <c r="E64" s="13" t="inlineStr">
-        <is>
-          <t>256→278</t>
-        </is>
-      </c>
+      <c r="A64" s="17" t="n"/>
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="17" t="n"/>
+      <c r="D64" s="17" t="n"/>
+      <c r="E64" s="17" t="n"/>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>휴젤</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H64" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-586170000</v>
+        <v>-2059070000</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>3.56%→2.47%</t>
+          <t>10.82%→10.23%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
         <is>
+          <t>236→216</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="19" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억   ·   현금 2억(0.6%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 11종목  /  매도 9종목</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="n"/>
+      <c r="I67" s="8" t="n"/>
+      <c r="J67" s="8" t="n"/>
+      <c r="K67" s="8" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>코미코  (신규)</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>357</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>671017200</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.47%</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>0→357</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="n">
+        <v>-71</v>
+      </c>
+      <c r="I69" s="15" t="n">
+        <v>-47338540</v>
+      </c>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>7.67%→7.30%</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>3,052→2,981</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>97</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>119513700</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>3.16%→3.52%</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>680→777</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>새로닉스</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <v>-44164680</v>
+      </c>
+      <c r="J70" s="16" t="inlineStr">
+        <is>
+          <t>3.08%→2.84%</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>907→858</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>노바렉스</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>67536840</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>0.16%→0.40%</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>51→133</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>-37</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>-104454700</v>
+      </c>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>8.09%→7.51%</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>761→724</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>42430860</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>0.28%→0.43%</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>122→191</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>-35</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>-93758000</v>
+      </c>
+      <c r="J72" s="16" t="inlineStr">
+        <is>
+          <t>3.38%→2.95%</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>335→300</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>스피어</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>44348200</v>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>2.36%→2.46%</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>367→393</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>-23776200</v>
+      </c>
+      <c r="J73" s="16" t="inlineStr">
+        <is>
+          <t>0.60%→0.50%</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>227→193</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>53235600</v>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>2.80%→2.93%</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>307→329</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I74" s="15" t="n">
+        <v>-87823200</v>
+      </c>
+      <c r="J74" s="16" t="inlineStr">
+        <is>
+          <t>1.06%→0.71%</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>77→53</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱  (신규)</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>118030000</v>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.43%</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>0→22</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="n">
+        <v>-17</v>
+      </c>
+      <c r="I75" s="15" t="n">
+        <v>-72083400</v>
+      </c>
+      <c r="J75" s="16" t="inlineStr">
+        <is>
+          <t>0.48%→0.20%</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t>30→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>41558400</v>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>1.02%→1.15%</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>104→120</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I76" s="15" t="n">
+        <v>-52036800</v>
+      </c>
+      <c r="J76" s="16" t="inlineStr">
+        <is>
+          <t>1.48%→1.25%</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="inlineStr">
+        <is>
+          <t>121→105</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>54182800</v>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>1.02%→1.19%</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>35→42</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I77" s="15" t="n">
+        <v>-34232400</v>
+      </c>
+      <c r="J77" s="16" t="inlineStr">
+        <is>
+          <t>1.76%→1.59%</t>
+        </is>
+      </c>
+      <c r="K77" s="13" t="inlineStr">
+        <is>
+          <t>41→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>40774000</v>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>3.13%→3.21%</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>102→107</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="n"/>
+      <c r="H78" s="17" t="n"/>
+      <c r="I78" s="17" t="n"/>
+      <c r="J78" s="17" t="n"/>
+      <c r="K78" s="17" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>보로노이  (신규)</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>24804800</v>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.09%</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>0→2</t>
+        </is>
+      </c>
+      <c r="G79" s="17" t="n"/>
+      <c r="H79" s="17" t="n"/>
+      <c r="I79" s="17" t="n"/>
+      <c r="J79" s="17" t="n"/>
+      <c r="K79" s="17" t="n"/>
+    </row>
+    <row r="81" ht="19" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 560억   ·   현금 3억(0.5%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 4종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="n"/>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="n"/>
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="n"/>
+      <c r="G81" s="4" t="n"/>
+      <c r="H81" s="4" t="n"/>
+      <c r="I81" s="4" t="n"/>
+      <c r="J81" s="4" t="n"/>
+      <c r="K81" s="4" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="n"/>
+      <c r="C82" s="6" t="n"/>
+      <c r="D82" s="6" t="n"/>
+      <c r="E82" s="6" t="n"/>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="n"/>
+      <c r="I82" s="8" t="n"/>
+      <c r="J82" s="8" t="n"/>
+      <c r="K82" s="8" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K83" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>프로티나  (신규)</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="n">
+        <v>227</v>
+      </c>
+      <c r="C84" s="11" t="n">
+        <v>928237050</v>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.70%</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="inlineStr">
+        <is>
+          <t>0→227</t>
+        </is>
+      </c>
+      <c r="G84" s="14" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="H84" s="15" t="n">
+        <v>-230</v>
+      </c>
+      <c r="I84" s="15" t="n">
+        <v>-523937700</v>
+      </c>
+      <c r="J84" s="16" t="inlineStr">
+        <is>
+          <t>2.62%→0.98%</t>
+        </is>
+      </c>
+      <c r="K84" s="13" t="inlineStr">
+        <is>
+          <t>464→234</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="n">
+        <v>223</v>
+      </c>
+      <c r="C85" s="11" t="n">
+        <v>432066960</v>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>2.52%→3.11%</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>655→878</t>
+        </is>
+      </c>
+      <c r="G85" s="14" t="inlineStr">
+        <is>
+          <t>리브스메드</t>
+        </is>
+      </c>
+      <c r="H85" s="15" t="n">
+        <v>-116</v>
+      </c>
+      <c r="I85" s="15" t="n">
+        <v>-472305600</v>
+      </c>
+      <c r="J85" s="16" t="inlineStr">
+        <is>
+          <t>2.90%→1.74%</t>
+        </is>
+      </c>
+      <c r="K85" s="13" t="inlineStr">
+        <is>
+          <t>349→233</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="C86" s="11" t="n">
+        <v>276623100</v>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>3.42%→3.91%</t>
+        </is>
+      </c>
+      <c r="E86" s="13" t="inlineStr">
+        <is>
+          <t>498→572</t>
+        </is>
+      </c>
+      <c r="G86" s="14" t="inlineStr">
+        <is>
+          <t>한스바이오메드</t>
+        </is>
+      </c>
+      <c r="H86" s="15" t="n">
+        <v>-91</v>
+      </c>
+      <c r="I86" s="15" t="n">
+        <v>-201973590</v>
+      </c>
+      <c r="J86" s="16" t="inlineStr">
+        <is>
+          <t>1.77%→1.26%</t>
+        </is>
+      </c>
+      <c r="K86" s="13" t="inlineStr">
+        <is>
+          <t>402→311</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C87" s="11" t="n">
+        <v>274645800</v>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>5.50%→6.35%</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>256→278</t>
+        </is>
+      </c>
+      <c r="G87" s="14" t="inlineStr">
+        <is>
+          <t>휴젤</t>
+        </is>
+      </c>
+      <c r="H87" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I87" s="15" t="n">
+        <v>-581490000</v>
+      </c>
+      <c r="J87" s="16" t="inlineStr">
+        <is>
+          <t>3.56%→2.50%</t>
+        </is>
+      </c>
+      <c r="K87" s="13" t="inlineStr">
+        <is>
           <t>67→47</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="19" customHeight="1">
-      <c r="A66" s="18" t="inlineStr">
+    <row r="89" ht="19" customHeight="1">
+      <c r="A89" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B66" s="19" t="n"/>
-      <c r="C66" s="19" t="n"/>
-      <c r="D66" s="19" t="n"/>
-      <c r="E66" s="19" t="n"/>
-      <c r="F66" s="19" t="n"/>
-      <c r="G66" s="19" t="n"/>
-      <c r="H66" s="19" t="n"/>
-      <c r="I66" s="19" t="n"/>
-      <c r="J66" s="19" t="n"/>
-      <c r="K66" s="19" t="n"/>
+      <c r="B89" s="19" t="n"/>
+      <c r="C89" s="19" t="n"/>
+      <c r="D89" s="19" t="n"/>
+      <c r="E89" s="19" t="n"/>
+      <c r="F89" s="19" t="n"/>
+      <c r="G89" s="19" t="n"/>
+      <c r="H89" s="19" t="n"/>
+      <c r="I89" s="19" t="n"/>
+      <c r="J89" s="19" t="n"/>
+      <c r="K89" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A58:K58"/>
+  <mergeCells count="21">
+    <mergeCell ref="G52:K52"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="G67:K67"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G82:K82"/>
+    <mergeCell ref="A66:K66"/>
+    <mergeCell ref="A89:K89"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="G29:K29"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G59:K59"/>
-    <mergeCell ref="A39:K39"/>
-    <mergeCell ref="A66:K66"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G44:K44"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A81:K81"/>
     <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="G40:K40"/>
+    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260826.xlsx
+++ b/reports/pdf_rolling5_20260826.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,456억   ·   현금 81억(1.7%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 10종목  /  매도 21종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,456억   ·   현금 40억(0.9%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 10종목  /  매도 21종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1243,23 +1243,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-212334500</v>
+        <v>-936579000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.51%</t>
+          <t>2.30%→2.02%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>83→76</t>
+          <t>76→69</t>
         </is>
       </c>
     </row>
@@ -1271,23 +1271,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-936579000</v>
+        <v>-212334500</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>2.30%→2.02%</t>
+          <t>0.58%→0.51%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>76→69</t>
+          <t>83→76</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,915억   ·   현금 38억(1.0%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 7종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,915억   ·   현금 19억(0.5%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 7종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1739,7 +1739,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억   ·   현금 64억(2.4%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 6종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억   ·   현금 32억(1.2%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 6종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>
@@ -2148,7 +2148,7 @@
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,255억   ·   현금 63억(2.8%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 4종목  /  매도 11종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,255억   ·   현금 32억(1.4%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 4종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B51" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260826.xlsx
+++ b/reports/pdf_rolling5_20260826.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,456억   ·   현금 40억(0.9%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 10종목  /  매도 21종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,588억   ·   현금 40억(0.9%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 10종목  /  매도 21종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1131,23 +1131,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-433836000</v>
+        <v>-1444884000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.50%→1.28%</t>
+          <t>4.68%→4.54%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>184→172</t>
         </is>
       </c>
     </row>
@@ -1159,23 +1159,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1444884000</v>
+        <v>-433836000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>4.68%→4.54%</t>
+          <t>1.50%→1.28%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>184→172</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
@@ -1327,23 +1327,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1313250000</v>
+        <v>-451655000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>3.52%→2.88%</t>
+          <t>0.62%→0.51%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>31→26</t>
         </is>
       </c>
     </row>
@@ -1355,23 +1355,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-451655000</v>
+        <v>-1313250000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.62%→0.51%</t>
+          <t>3.52%→2.88%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>31→26</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,915억   ·   현금 19억(0.5%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 7종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,836억   ·   현금 19억(0.5%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 7종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1502,7 +1502,7 @@
         <v>140</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1217160000</v>
+        <v>1224115200</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>-527</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-4401899250</v>
+        <v>-4427052960</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>69</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>705300750</v>
+        <v>709331040</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>-32</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-353640000</v>
+        <v>-355660800</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>50</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>742875000</v>
+        <v>747120000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>-6</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-962325000</v>
+        <v>-967824000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>24</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>764820000</v>
+        <v>769190400</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>18</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>704970000</v>
+        <v>708998400</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>13</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>685230000</v>
+        <v>689145600</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>3</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>652837500</v>
+        <v>656568000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억   ·   현금 32억(1.2%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 6종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,606억   ·   현금 32억(1.2%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 6종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>
@@ -1835,7 +1835,7 @@
         <v>110</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>3127410000</v>
+        <v>3114045000</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>-158</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-1497366000</v>
+        <v>-1490967000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>61</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>5005891800</v>
+        <v>4984499100</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>-144</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-898672320</v>
+        <v>-894831840</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>21</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1480096800</v>
+        <v>1473771600</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>-116</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-785818800</v>
+        <v>-782460600</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>20</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>3495960000</v>
+        <v>3481020000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>-77</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-640539900</v>
+        <v>-637802550</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>13</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>179599680</v>
+        <v>178832160</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>-50</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-738855000</v>
+        <v>-735697500</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>12</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>3382236000</v>
+        <v>3367782000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>-49</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-2211791400</v>
+        <v>-2202339300</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>-42</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-1500735600</v>
+        <v>-1494322200</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>-35</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-7506135000</v>
+        <v>-7474057500</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,255억   ·   현금 32억(1.4%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 4종목  /  매도 11종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,218억   ·   현금 32억(1.4%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 4종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B51" s="4" t="n"/>
@@ -2244,7 +2244,7 @@
         <v>296</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>6054946400</v>
+        <v>6072913600</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>-218</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-1430383020</v>
+        <v>-1434627480</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>279</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>6647426100</v>
+        <v>6667151400</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>-194</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-1980953400</v>
+        <v>-1986831600</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>56</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>3172383200</v>
+        <v>3181796800</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>-183</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-6580295700</v>
+        <v>-6599821800</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>24</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>4052088000</v>
+        <v>4064112000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>-125</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-4199862500</v>
+        <v>-4212325000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>-102</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1904319600</v>
+        <v>-1909970400</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>-101</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-884962000</v>
+        <v>-887588000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>-80</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-215680000</v>
+        <v>-216320000</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>-67</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-638985700</v>
+        <v>-640881800</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>-41</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-431781250</v>
+        <v>-433062500</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>-29</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-242859050</v>
+        <v>-243579700</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>-20</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-2059070000</v>
+        <v>-2065180000</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
     <row r="66" ht="19" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억   ·   현금 2억(0.6%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 11종목  /  매도 9종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 281억   ·   현금 2억(0.6%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 11종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B66" s="4" t="n"/>
@@ -2705,11 +2705,11 @@
         <v>357</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>671017200</v>
+        <v>684226200</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.47%</t>
+          <t>0.00%→2.45%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
@@ -2726,11 +2726,11 @@
         <v>-71</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-47338540</v>
+        <v>-45709800</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>7.67%→7.30%</t>
+          <t>7.22%→6.88%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -2749,11 +2749,11 @@
         <v>97</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>119513700</v>
+        <v>121738880</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>3.16%→3.52%</t>
+          <t>3.14%→3.50%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -2770,11 +2770,11 @@
         <v>-49</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-44164680</v>
+        <v>-44599800</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>3.08%→2.84%</t>
+          <t>3.03%→2.80%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
@@ -2793,11 +2793,11 @@
         <v>82</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>67536840</v>
+        <v>70206760</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>0.16%→0.40%</t>
+          <t>0.16%→0.41%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
@@ -2814,11 +2814,11 @@
         <v>-37</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-104454700</v>
+        <v>-105139200</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>8.09%→7.51%</t>
+          <t>7.95%→7.37%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
@@ -2837,7 +2837,7 @@
         <v>69</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>42430860</v>
+        <v>42992520</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
@@ -2858,11 +2858,11 @@
         <v>-35</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-93758000</v>
+        <v>-92981000</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>3.38%→2.95%</t>
+          <t>3.27%→2.86%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
@@ -2881,11 +2881,11 @@
         <v>26</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>44348200</v>
+        <v>45310200</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>2.36%→2.46%</t>
+          <t>2.35%→2.45%</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
@@ -2902,11 +2902,11 @@
         <v>-34</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-23776200</v>
+        <v>-24807760</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.50%</t>
+          <t>0.61%→0.50%</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr">
@@ -2918,23 +2918,23 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>오름테라퓨틱  (신규)</t>
         </is>
       </c>
       <c r="B74" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>53235600</v>
+        <v>115099600</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>2.80%→2.93%</t>
+          <t>0.00%→0.41%</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>307→329</t>
+          <t>0→22</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -2946,11 +2946,11 @@
         <v>-24</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-87823200</v>
+        <v>-92174400</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>1.06%→0.71%</t>
+          <t>1.09%→0.73%</t>
         </is>
       </c>
       <c r="K74" s="13" t="inlineStr">
@@ -2962,23 +2962,23 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>오름테라퓨틱  (신규)</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B75" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>118030000</v>
+        <v>58282400</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.43%</t>
+          <t>2.99%→3.12%</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>0→22</t>
+          <t>307→329</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
@@ -2990,11 +2990,11 @@
         <v>-17</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-72083400</v>
+        <v>-70699600</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.20%</t>
+          <t>0.46%→0.19%</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.15%</t>
+          <t>0.99%→1.12%</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
@@ -3034,11 +3034,11 @@
         <v>-16</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-52036800</v>
+        <v>-57424000</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>1.48%→1.25%</t>
+          <t>1.60%→1.35%</t>
         </is>
       </c>
       <c r="K76" s="13" t="inlineStr">
@@ -3057,11 +3057,11 @@
         <v>7</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>54182800</v>
+        <v>55736800</v>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.19%</t>
+          <t>1.02%→1.20%</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
@@ -3078,11 +3078,11 @@
         <v>-3</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>-34232400</v>
+        <v>-36696600</v>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>1.76%→1.59%</t>
+          <t>1.84%→1.67%</t>
         </is>
       </c>
       <c r="K77" s="13" t="inlineStr">
@@ -3101,11 +3101,11 @@
         <v>5</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>40774000</v>
+        <v>44659000</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>3.13%→3.21%</t>
+          <t>3.35%→3.43%</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
@@ -3129,7 +3129,7 @@
         <v>2</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>24804800</v>
+        <v>24878800</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
     <row r="81" ht="19" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 560억   ·   현금 3억(0.5%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 4종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 544억   ·   현금 3억(0.5%)      오늘 2026-08-26  vs  5일전 2026-08-19      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B81" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260826.xlsx
+++ b/reports/pdf_rolling5_20260826.xlsx
@@ -1131,23 +1131,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1444884000</v>
+        <v>-433836000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>4.68%→4.54%</t>
+          <t>1.50%→1.28%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>184→172</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
@@ -1159,23 +1159,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-433836000</v>
+        <v>-1444884000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.50%→1.28%</t>
+          <t>4.68%→4.54%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>184→172</t>
         </is>
       </c>
     </row>
@@ -1327,23 +1327,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-451655000</v>
+        <v>-1313250000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.62%→0.51%</t>
+          <t>3.52%→2.88%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>31→26</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
@@ -1355,23 +1355,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-1313250000</v>
+        <v>-451655000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>3.52%→2.88%</t>
+          <t>0.62%→0.51%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>31→26</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260826.xlsx
+++ b/reports/pdf_rolling5_20260826.xlsx
@@ -1131,23 +1131,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-433836000</v>
+        <v>-1444884000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.50%→1.28%</t>
+          <t>4.68%→4.54%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>184→172</t>
         </is>
       </c>
     </row>
@@ -1159,23 +1159,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1444884000</v>
+        <v>-433836000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>4.68%→4.54%</t>
+          <t>1.50%→1.28%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>184→172</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
@@ -1243,23 +1243,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-936579000</v>
+        <v>-212334500</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2.30%→2.02%</t>
+          <t>0.58%→0.51%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>76→69</t>
+          <t>83→76</t>
         </is>
       </c>
     </row>
@@ -1271,23 +1271,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-212334500</v>
+        <v>-936579000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.51%</t>
+          <t>2.30%→2.02%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>83→76</t>
+          <t>76→69</t>
         </is>
       </c>
     </row>
@@ -1327,23 +1327,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1313250000</v>
+        <v>-451655000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>3.52%→2.88%</t>
+          <t>0.62%→0.51%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>31→26</t>
         </is>
       </c>
     </row>
@@ -1355,23 +1355,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-451655000</v>
+        <v>-1313250000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.62%→0.51%</t>
+          <t>3.52%→2.88%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>31→26</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
@@ -2918,23 +2918,23 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>오름테라퓨틱  (신규)</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B74" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>115099600</v>
+        <v>58282400</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.41%</t>
+          <t>2.99%→3.12%</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>0→22</t>
+          <t>307→329</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -2962,23 +2962,23 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>오름테라퓨틱  (신규)</t>
         </is>
       </c>
       <c r="B75" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>58282400</v>
+        <v>115099600</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>2.99%→3.12%</t>
+          <t>0.00%→0.41%</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>307→329</t>
+          <t>0→22</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260826.xlsx
+++ b/reports/pdf_rolling5_20260826.xlsx
@@ -1243,23 +1243,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-212334500</v>
+        <v>-936579000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.51%</t>
+          <t>2.30%→2.02%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>83→76</t>
+          <t>76→69</t>
         </is>
       </c>
     </row>
@@ -1271,23 +1271,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-936579000</v>
+        <v>-212334500</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>2.30%→2.02%</t>
+          <t>0.58%→0.51%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>76→69</t>
+          <t>83→76</t>
         </is>
       </c>
     </row>
